--- a/data/dividends_info_20260313.xlsx
+++ b/data/dividends_info_20260313.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.65000152587891</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3820335220372</v>
+        <v>1.391650120511825</v>
       </c>
       <c r="J2" t="n">
         <v>346</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18.20000076293945</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>2.06593397933063</v>
+        <v>2.112359641101265</v>
       </c>
       <c r="J3" t="n">
         <v>129</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23.6200008392334</v>
+        <v>24.18000030517578</v>
       </c>
       <c r="I4" t="n">
-        <v>1.058425025898999</v>
+        <v>1.033912311185898</v>
       </c>
       <c r="J4" t="n">
         <v>101</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>22.29999923706055</v>
+        <v>22.04999923706055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8744394918001969</v>
+        <v>0.8843537720956184</v>
       </c>
       <c r="J5" t="n">
         <v>101</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>63.88000106811523</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9862241538290382</v>
+        <v>0.9831460393228127</v>
       </c>
       <c r="J6" t="n">
         <v>101</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>21.40999984741211</v>
+        <v>21.18000030517578</v>
       </c>
       <c r="I7" t="n">
-        <v>3.970107454730982</v>
+        <v>4.013219961060551</v>
       </c>
       <c r="J7" t="n">
         <v>101</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.467999935150146</v>
+        <v>6.613999843597412</v>
       </c>
       <c r="I8" t="n">
-        <v>2.803030331134215</v>
+        <v>2.74115519031203</v>
       </c>
       <c r="J8" t="n">
         <v>101</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10.39500045776367</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="I9" t="n">
-        <v>2.789802666948503</v>
+        <v>2.756653872443346</v>
       </c>
       <c r="J9" t="n">
         <v>66</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>33.63000106811523</v>
+        <v>34.20999908447266</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8765981204648</v>
+        <v>4.793920034754892</v>
       </c>
       <c r="J10" t="n">
         <v>66</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>32.63999938964844</v>
+        <v>32.13999938964844</v>
       </c>
       <c r="I11" t="n">
-        <v>6.127451094972407</v>
+        <v>6.222775475982599</v>
       </c>
       <c r="J11" t="n">
         <v>66</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.917999982833862</v>
+        <v>3.865999937057495</v>
       </c>
       <c r="I12" t="n">
-        <v>2.552322624760981</v>
+        <v>2.58665291329809</v>
       </c>
       <c r="J12" t="n">
         <v>66</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>33.79999923706055</v>
+        <v>36.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4392307791451625</v>
+        <v>0.4067397260273973</v>
       </c>
       <c r="J13" t="n">
         <v>66</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.09999847412109</v>
+        <v>70.33999633789062</v>
       </c>
       <c r="I14" t="n">
-        <v>1.442441084618453</v>
+        <v>1.478532917465869</v>
       </c>
       <c r="J14" t="n">
         <v>66</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50.65000152587891</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>4.34353392640263</v>
+        <v>4.373757521608592</v>
       </c>
       <c r="J15" t="n">
         <v>66</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7.159999847412109</v>
+        <v>7.13700008392334</v>
       </c>
       <c r="I16" t="n">
-        <v>12.01117344032956</v>
+        <v>12.04988076064646</v>
       </c>
       <c r="J16" t="n">
         <v>66</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11.03999996185303</v>
+        <v>10.97000026702881</v>
       </c>
       <c r="I17" t="n">
-        <v>5.072463785643038</v>
+        <v>5.104831233989334</v>
       </c>
       <c r="J17" t="n">
         <v>66</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14.5</v>
+        <v>14.52000045776367</v>
       </c>
       <c r="I19" t="n">
-        <v>2.068965517241379</v>
+        <v>2.066115637342102</v>
       </c>
       <c r="J19" t="n">
         <v>66</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>22.55999946594238</v>
+        <v>21.78000068664551</v>
       </c>
       <c r="I20" t="n">
-        <v>4.432624218407656</v>
+        <v>4.591368082982449</v>
       </c>
       <c r="J20" t="n">
         <v>66</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19.08499908447266</v>
+        <v>18.69499969482422</v>
       </c>
       <c r="I22" t="n">
-        <v>4.139376672240635</v>
+        <v>4.225728873473662</v>
       </c>
       <c r="J22" t="n">
         <v>66</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.215000152587891</v>
+        <v>5.144000053405762</v>
       </c>
       <c r="I23" t="n">
-        <v>3.643336422640648</v>
+        <v>3.693623600843549</v>
       </c>
       <c r="J23" t="n">
         <v>66</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>10.14999961853027</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I24" t="n">
-        <v>4.256157795428113</v>
+        <v>4.235294196844927</v>
       </c>
       <c r="J24" t="n">
         <v>66</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>24.65999984741211</v>
+        <v>24.78000068664551</v>
       </c>
       <c r="I25" t="n">
-        <v>1.784266028883106</v>
+        <v>1.775625455237077</v>
       </c>
       <c r="J25" t="n">
         <v>66</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>52.93999862670898</v>
+        <v>52.56000137329102</v>
       </c>
       <c r="I26" t="n">
-        <v>2.644503279782255</v>
+        <v>2.663622457040928</v>
       </c>
       <c r="J26" t="n">
         <v>66</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.956000089645386</v>
+        <v>2.983000040054321</v>
       </c>
       <c r="I27" t="n">
-        <v>10.14884948924306</v>
+        <v>10.05698947273688</v>
       </c>
       <c r="J27" t="n">
         <v>66</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>82.09999847412109</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="I28" t="n">
-        <v>1.644336205956857</v>
+        <v>1.549053329160438</v>
       </c>
       <c r="J28" t="n">
         <v>66</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.288000106811523</v>
+        <v>3.36899995803833</v>
       </c>
       <c r="I29" t="n">
-        <v>5.170316133744118</v>
+        <v>5.046007780272756</v>
       </c>
       <c r="J29" t="n">
         <v>66</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.889999866485596</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8179959323546503</v>
+        <v>0.8830021666090007</v>
       </c>
       <c r="J30" t="n">
         <v>66</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29.89999961853027</v>
+        <v>29.64999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>3.51170573042172</v>
+        <v>3.541315391261539</v>
       </c>
       <c r="J31" t="n">
         <v>66</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23.20000076293945</v>
+        <v>23.04000091552734</v>
       </c>
       <c r="I32" t="n">
-        <v>2.586206811503482</v>
+        <v>2.604166563186384</v>
       </c>
       <c r="J32" t="n">
         <v>66</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.711999893188477</v>
+        <v>2.476000070571899</v>
       </c>
       <c r="I33" t="n">
-        <v>9.587021026550266</v>
+        <v>10.50080745514462</v>
       </c>
       <c r="J33" t="n">
         <v>66</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7.309999942779541</v>
+        <v>6.809999942779541</v>
       </c>
       <c r="I34" t="n">
-        <v>3.009575946950659</v>
+        <v>3.230543345793418</v>
       </c>
       <c r="J34" t="n">
         <v>59</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.595000028610229</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="I35" t="n">
-        <v>4.450625833843276</v>
+        <v>4.481792800894103</v>
       </c>
       <c r="J35" t="n">
         <v>52</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19.55999946594238</v>
+        <v>18.3799991607666</v>
       </c>
       <c r="I36" t="n">
-        <v>3.118609492102104</v>
+        <v>3.318824961113642</v>
       </c>
       <c r="J36" t="n">
         <v>52</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8.520000457763672</v>
+        <v>8.510000228881836</v>
       </c>
       <c r="I37" t="n">
-        <v>5.991783715631348</v>
+        <v>5.998824750526201</v>
       </c>
       <c r="J37" t="n">
         <v>52</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7.039999961853027</v>
+        <v>6.949999809265137</v>
       </c>
       <c r="I38" t="n">
-        <v>3.835227293508851</v>
+        <v>3.884892192947393</v>
       </c>
       <c r="J38" t="n">
         <v>52</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4.820000171661377</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I39" t="n">
-        <v>7.261410529771011</v>
+        <v>7.743362864533833</v>
       </c>
       <c r="J39" t="n">
         <v>52</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>18.70000076293945</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I40" t="n">
-        <v>4.010695023533825</v>
+        <v>3.989361864023487</v>
       </c>
       <c r="J40" t="n">
         <v>52</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.44999980926514</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I41" t="n">
-        <v>4.114832610989668</v>
+        <v>4.174757204245461</v>
       </c>
       <c r="J41" t="n">
         <v>52</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.954999923706055</v>
+        <v>3.964999914169312</v>
       </c>
       <c r="I42" t="n">
-        <v>3.792667582644139</v>
+        <v>3.783102225651013</v>
       </c>
       <c r="J42" t="n">
         <v>52</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>11.72000026702881</v>
+        <v>11.47999954223633</v>
       </c>
       <c r="I43" t="n">
-        <v>1.682329313205598</v>
+        <v>1.717500068485116</v>
       </c>
       <c r="J43" t="n">
         <v>52</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>25.54999923706055</v>
+        <v>25.25</v>
       </c>
       <c r="I44" t="n">
-        <v>4.305283885897102</v>
+        <v>4.356435643564357</v>
       </c>
       <c r="J44" t="n">
         <v>52</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10.14999961853027</v>
+        <v>10.25</v>
       </c>
       <c r="I45" t="n">
-        <v>3.743842505237692</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J45" t="n">
         <v>52</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>27.85000038146973</v>
+        <v>28</v>
       </c>
       <c r="I46" t="n">
-        <v>1.077199267112427</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="J46" t="n">
         <v>52</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.980000019073486</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I47" t="n">
-        <v>2.675585275747034</v>
+        <v>2.768165989483679</v>
       </c>
       <c r="J47" t="n">
         <v>45</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.230000019073486</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I48" t="n">
-        <v>2.914798181347371</v>
+        <v>2.941176419820373</v>
       </c>
       <c r="J48" t="n">
         <v>45</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7.559999942779541</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I49" t="n">
-        <v>3.306878331907552</v>
+        <v>3.491620186142313</v>
       </c>
       <c r="J49" t="n">
         <v>45</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.644999980926514</v>
+        <v>6.614999771118164</v>
       </c>
       <c r="I50" t="n">
-        <v>7.524454498648243</v>
+        <v>7.558579248680498</v>
       </c>
       <c r="J50" t="n">
         <v>38</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11.41499996185303</v>
+        <v>11.43000030517578</v>
       </c>
       <c r="I51" t="n">
-        <v>4.7306176242189</v>
+        <v>4.724409322679326</v>
       </c>
       <c r="J51" t="n">
         <v>38</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6.165999889373779</v>
+        <v>6.176000118255615</v>
       </c>
       <c r="I52" t="n">
-        <v>1.621796980118922</v>
+        <v>1.619170953452711</v>
       </c>
       <c r="J52" t="n">
         <v>38</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10.44999980926514</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I53" t="n">
-        <v>1.53110050641476</v>
+        <v>1.758241684536706</v>
       </c>
       <c r="J53" t="n">
         <v>38</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>292.6000061035156</v>
+        <v>289.2000122070312</v>
       </c>
       <c r="I54" t="n">
-        <v>1.235475025493024</v>
+        <v>1.249999947237938</v>
       </c>
       <c r="J54" t="n">
         <v>38</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>26.70000076293945</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I55" t="n">
-        <v>5.09363281325343</v>
+        <v>5.151515225952543</v>
       </c>
       <c r="J55" t="n">
         <v>38</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>13.32999992370605</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="I56" t="n">
-        <v>4.388597174405356</v>
+        <v>4.545454585873038</v>
       </c>
       <c r="J56" t="n">
         <v>38</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>15.86499977111816</v>
+        <v>15.77000045776367</v>
       </c>
       <c r="I57" t="n">
-        <v>3.971005414994706</v>
+        <v>3.994926960765223</v>
       </c>
       <c r="J57" t="n">
         <v>38</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>101.5500030517578</v>
+        <v>98.41999816894531</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8862628980338776</v>
+        <v>0.914448299882187</v>
       </c>
       <c r="J58" t="n">
         <v>38</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65.06999969482422</v>
+        <v>63.5</v>
       </c>
       <c r="I59" t="n">
-        <v>2.644536665238183</v>
+        <v>2.70992125984252</v>
       </c>
       <c r="J59" t="n">
         <v>38</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>22.79999923706055</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6140351082662987</v>
+        <v>0.6306306089579743</v>
       </c>
       <c r="J60" t="n">
         <v>31</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.5</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3.973509958870426</v>
       </c>
       <c r="J61" t="n">
         <v>31</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.940000057220459</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I62" t="n">
-        <v>1.752577267895219</v>
+        <v>1.7616580789651</v>
       </c>
       <c r="J62" t="n">
         <v>17</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>21.76499938964844</v>
+        <v>22.35000038146973</v>
       </c>
       <c r="I63" t="n">
-        <v>1.194578485141872</v>
+        <v>1.163310942113293</v>
       </c>
       <c r="J63" t="n">
         <v>10</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>28.95999908447266</v>
+        <v>28.61499977111816</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3107734904876253</v>
+        <v>0.3145203589721474</v>
       </c>
       <c r="J64" t="n">
         <v>10</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>50.65000152587891</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I65" t="n">
-        <v>1.283316841891686</v>
+        <v>1.292246540475266</v>
       </c>
       <c r="J65" t="n">
         <v>-18</v>
@@ -3507,7 +3507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C311"/>
+  <dimension ref="A1:C321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3751,7 +3751,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3785,7 +3785,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3795,14 +3795,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3812,14 +3812,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3829,14 +3829,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3846,14 +3846,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4244,7 +4244,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4261,7 +4261,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4407,14 +4407,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4465,7 +4465,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4533,7 +4533,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4543,14 +4543,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4567,7 +4567,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4577,14 +4577,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4594,14 +4594,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4628,14 +4628,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4696,14 +4696,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4720,7 +4720,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4924,7 +4924,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4941,7 +4941,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4958,7 +4958,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4975,7 +4975,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5002,14 +5002,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5043,7 +5043,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5189,14 +5189,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5230,7 +5230,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5240,14 +5240,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5264,7 +5264,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5281,7 +5281,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5315,7 +5315,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5332,7 +5332,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5366,7 +5366,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5417,7 +5417,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5478,14 +5478,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5495,14 +5495,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5546,14 +5546,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5563,14 +5563,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5587,7 +5587,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5604,7 +5604,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5621,7 +5621,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5638,7 +5638,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5655,7 +5655,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5672,7 +5672,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5689,7 +5689,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5699,14 +5699,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5716,14 +5716,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5740,7 +5740,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5784,14 +5784,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5818,14 +5818,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5876,7 +5876,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5910,7 +5910,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5944,7 +5944,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5961,7 +5961,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5978,7 +5978,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5988,14 +5988,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6012,7 +6012,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6029,7 +6029,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6039,14 +6039,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6114,7 +6114,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6124,14 +6124,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6165,7 +6165,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6182,7 +6182,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6199,7 +6199,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6284,7 +6284,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6301,7 +6301,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6335,7 +6335,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6345,14 +6345,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6369,7 +6369,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6386,7 +6386,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6403,7 +6403,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6488,7 +6488,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6498,14 +6498,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6522,7 +6522,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6539,7 +6539,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6573,7 +6573,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6590,7 +6590,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6607,7 +6607,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6641,7 +6641,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6658,7 +6658,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6675,7 +6675,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6692,7 +6692,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6726,7 +6726,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6743,7 +6743,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6760,7 +6760,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6811,7 +6811,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6828,7 +6828,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6845,7 +6845,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6879,7 +6879,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6906,14 +6906,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6930,7 +6930,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6947,7 +6947,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6964,7 +6964,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6981,7 +6981,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7015,7 +7015,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7025,14 +7025,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7066,7 +7066,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7083,7 +7083,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7100,12 +7100,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7117,7 +7117,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7134,7 +7134,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7151,7 +7151,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7185,7 +7185,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7202,7 +7202,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7219,7 +7219,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7253,7 +7253,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7270,7 +7270,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7280,14 +7280,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7304,7 +7304,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7321,7 +7321,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7338,7 +7338,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7372,7 +7372,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7389,7 +7389,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7406,7 +7406,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7423,7 +7423,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7440,7 +7440,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7457,7 +7457,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7474,7 +7474,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7491,7 +7491,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7525,7 +7525,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7559,7 +7559,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7576,7 +7576,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7593,7 +7593,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7610,7 +7610,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7627,7 +7627,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7644,7 +7644,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7661,7 +7661,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7678,7 +7678,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7729,7 +7729,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7746,7 +7746,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7763,7 +7763,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7797,7 +7797,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7814,7 +7814,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7824,14 +7824,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7848,12 +7848,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7865,46 +7865,46 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7916,12 +7916,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7933,12 +7933,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7950,12 +7950,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7967,12 +7967,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7984,41 +7984,41 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8035,7 +8035,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8069,7 +8069,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8103,7 +8103,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8120,7 +8120,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8137,7 +8137,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8164,14 +8164,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8188,7 +8188,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8198,14 +8198,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8239,7 +8239,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8256,7 +8256,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8273,7 +8273,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8283,14 +8283,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8307,7 +8307,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8324,7 +8324,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8358,7 +8358,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8375,7 +8375,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8392,7 +8392,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8426,7 +8426,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8436,14 +8436,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8460,7 +8460,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8470,70 +8470,70 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8545,182 +8545,182 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8732,12 +8732,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8749,49 +8749,219 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
+          <t>Gas Plus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Gas Plus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>BORGOSESIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Indel B S.p.A.</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Growens S.p.A.</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>DESTINATION ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Masi Agricola S.p.A.</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
           <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
+      <c r="C321" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -8808,818 +8978,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001207098</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>23.6200008392334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.058425025898999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>101</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0004093263</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3.595000028610229</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4.450625833843276</v>
-      </c>
-      <c r="I3" t="n">
-        <v>52</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0000062072</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>33.63000106811523</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4.8765981204648</v>
-      </c>
-      <c r="I4" t="n">
-        <v>66</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Alerion Clean Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0004720733</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>19.55999946594238</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3.118609492102104</v>
-      </c>
-      <c r="I5" t="n">
-        <v>52</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Avio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005119810</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>33.79999923706055</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.14846</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.4392307791451625</v>
-      </c>
-      <c r="I6" t="n">
-        <v>66</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0000066123</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>11.03999996185303</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5.072463785643038</v>
-      </c>
-      <c r="I7" t="n">
-        <v>66</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NL0013995087</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2.068965517241379</v>
-      </c>
-      <c r="I8" t="n">
-        <v>66</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LU2592315662</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7.039999961853027</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>3.835227293508851</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IT0001157020</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22.55999946594238</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>4.432624218407656</v>
-      </c>
-      <c r="I10" t="n">
-        <v>66</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Enervit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IT0004356751</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4.099999904632568</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>5.243902560999395</v>
-      </c>
-      <c r="I11" t="n">
-        <v>66</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IT0003850929</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4.820000171661377</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>7.261410529771011</v>
-      </c>
-      <c r="I12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IT0005215329</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-04-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>10.44999980926514</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1.53110050641476</v>
-      </c>
-      <c r="I13" t="n">
-        <v>38</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IT0003365613</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-04-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>7.559999942779541</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>3.306878331907552</v>
-      </c>
-      <c r="I14" t="n">
-        <v>45</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GEFRAN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>IT0003203947</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>10.44999980926514</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>4.114832610989668</v>
-      </c>
-      <c r="I15" t="n">
-        <v>52</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Leonardo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>IT0003856405</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>63.88000106811523</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.9862241538290382</v>
-      </c>
-      <c r="I16" t="n">
-        <v>101</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>IT0005282865</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>82.09999847412109</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1.644336205956857</v>
-      </c>
-      <c r="I17" t="n">
-        <v>66</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>WEBUILD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>IT0003865570</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2.711999893188477</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>9.587021026550266</v>
-      </c>
-      <c r="I18" t="n">
-        <v>66</v>
-      </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>IT0004171440</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>7.309999942779541</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>3.009575946950659</v>
-      </c>
-      <c r="I19" t="n">
-        <v>59</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9630,61 +8991,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CULTI Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>